--- a/data/trans_bre/P6901-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 17,84</t>
+          <t>-19,35; 18,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 48,15</t>
+          <t>-29,67; 41,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 65,61</t>
+          <t>8,84; 65,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-75,52; -8,4</t>
+          <t>-69,52; -7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 23,54</t>
+          <t>-22,15; 24,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 110,04</t>
+          <t>-32,33; 93,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,6; 246,2</t>
+          <t>14,67; 231,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-75,52; -8,4</t>
+          <t>-69,52; -7,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 15,6</t>
+          <t>-9,29; 14,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 15,24</t>
+          <t>-12,72; 14,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 20,78</t>
+          <t>-1,71; 20,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 3,05</t>
+          <t>-34,34; 1,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 23,52</t>
+          <t>-12,84; 22,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 21,62</t>
+          <t>-15,33; 21,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 27,68</t>
+          <t>-1,73; 28,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 4,12</t>
+          <t>-40,01; 0,56</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 23,33</t>
+          <t>-1,97; 22,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 23,16</t>
+          <t>-4,47; 22,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 15,58</t>
+          <t>-9,01; 15,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 13,77</t>
+          <t>-9,9; 13,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 38,31</t>
+          <t>-2,73; 36,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 36,72</t>
+          <t>-5,5; 36,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 21,07</t>
+          <t>-11,17; 21,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 19,51</t>
+          <t>-11,92; 18,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 19,04</t>
+          <t>-10,45; 19,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 7,92</t>
+          <t>-30,3; 7,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 29,54</t>
+          <t>-2,08; 27,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 29,73</t>
+          <t>1,99; 28,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 27,31</t>
+          <t>-12,31; 28,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 10,51</t>
+          <t>-37,71; 9,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 51,8</t>
+          <t>-2,75; 45,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 50,59</t>
+          <t>2,54; 50,15</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -4,41</t>
+          <t>-60,08; -2,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 32,55</t>
+          <t>-2,05; 31,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 23,78</t>
+          <t>-12,84; 25,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 27,6</t>
+          <t>1,09; 28,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-59,71; -5,56</t>
+          <t>-63,71; -3,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 52,75</t>
+          <t>-1,95; 50,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 35,38</t>
+          <t>-13,89; 38,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 50,17</t>
+          <t>1,78; 50,1</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 63,49</t>
+          <t>-37,62; 64,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,81; 205,87</t>
+          <t>-39,33; 247,74</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,7</t>
+          <t>-3,94; 9,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 11,08</t>
+          <t>-3,46; 10,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 16,95</t>
+          <t>3,66; 17,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 13,76</t>
+          <t>-3,01; 13,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 13,49</t>
+          <t>-5,03; 13,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 15,56</t>
+          <t>-4,45; 15,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 24,51</t>
+          <t>4,84; 24,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 20,14</t>
+          <t>-3,74; 18,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6901-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-33,03</t>
+          <t>-29,68</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-33,03%</t>
+          <t>-29,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 18,28</t>
+          <t>-18,06; 19,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 41,46</t>
+          <t>-28,9; 45,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 65,99</t>
+          <t>11,49; 65,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-69,52; -7,4</t>
+          <t>-69,27; -7,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 24,96</t>
+          <t>-20,89; 25,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 93,6</t>
+          <t>-30,99; 102,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,67; 231,15</t>
+          <t>16,01; 236,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-69,52; -7,4</t>
+          <t>-69,27; -7,04</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-18,32</t>
+          <t>-20,05</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-22,25%</t>
+          <t>-23,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 14,83</t>
+          <t>-10,04; 15,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 14,92</t>
+          <t>-11,97; 15,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 20,67</t>
+          <t>-1,91; 21,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 1,35</t>
+          <t>-36,76; -1,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 22,36</t>
+          <t>-13,42; 23,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 21,07</t>
+          <t>-14,54; 22,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 28,44</t>
+          <t>-1,51; 28,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 0,56</t>
+          <t>-40,31; -2,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,28</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 22,77</t>
+          <t>-2,5; 21,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 22,6</t>
+          <t>-7,44; 21,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 15,97</t>
+          <t>-8,6; 15,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 13,37</t>
+          <t>-9,29; 13,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 36,58</t>
+          <t>-3,33; 34,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 36,12</t>
+          <t>-9,64; 34,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 21,68</t>
+          <t>-10,65; 21,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 18,7</t>
+          <t>-11,28; 19,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,0</t>
+          <t>11,94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 19,7</t>
+          <t>-9,86; 19,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 7,28</t>
+          <t>-28,48; 7,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 27,17</t>
+          <t>-1,85; 28,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 28,71</t>
+          <t>1,97; 23,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 28,1</t>
+          <t>-12,26; 27,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 9,9</t>
+          <t>-36,5; 10,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 45,81</t>
+          <t>-1,95; 50,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 50,15</t>
+          <t>2,73; 39,07</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>13,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-60,08; -2,92</t>
+          <t>-54,28; -1,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 31,26</t>
+          <t>-1,54; 35,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 25,94</t>
+          <t>-12,43; 25,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 28,28</t>
+          <t>1,17; 26,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,71; -3,54</t>
+          <t>-59,3; -2,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 50,48</t>
+          <t>-1,31; 57,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 38,78</t>
+          <t>-14,47; 37,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 50,1</t>
+          <t>1,52; 44,65</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,98</t>
+          <t>4,86</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,62; 64,71</t>
+          <t>-37,2; 64,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 247,74</t>
+          <t>-38,93; 184,51</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,67</t>
+          <t>-3,69; 9,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,73</t>
+          <t>-4,49; 11,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 17,31</t>
+          <t>3,19; 17,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 13,01</t>
+          <t>-3,92; 8,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 13,3</t>
+          <t>-4,71; 13,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,32</t>
+          <t>-6,04; 16,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,84; 24,41</t>
+          <t>3,99; 24,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 18,93</t>
+          <t>-5,08; 12,12</t>
         </is>
       </c>
     </row>
